--- a/bibliography/master-bibliography.xlsx
+++ b/bibliography/master-bibliography.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master bibliography" sheetId="1" r:id="Rb298d4a6e63347ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R349c6b97d37a4efd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review notes" sheetId="3" r:id="R65a1ed35337d40ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master bibliography" sheetId="1" r:id="R3b9c728fb3124e1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R142d6446af554a4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review notes" sheetId="3" r:id="R316eaa58647c4118"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -71,62 +71,22 @@
   <x:borders count="18">
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:left/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:left/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:left/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -279,7 +239,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MasterBibliography" displayName="MasterBibliography" ref="A4:N70" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MasterBibliography" displayName="MasterBibliography" ref="A4:N73" headerRowCount="1">
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Title"/>
@@ -485,7 +445,7 @@
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>Consolidated from 11 reviewed batches; 66 bibliography entries. Nuclear-analogy articles are excluded as requested.</x:v>
+        <x:v>Consolidated bibliography with 69 entries. Nuclear-analogy articles are excluded as requested.</x:v>
       </x:c>
       <x:c r="B2" s="12"/>
       <x:c r="C2" s="12"/>
@@ -3229,6 +3189,124 @@
         <x:v>https://astrangeattractor.substack.com/p/components-of-a-frontier-ai-slowdown</x:v>
       </x:c>
     </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="str">
+        <x:v>ammann-faster-ai-diffusion-hardware-verification</x:v>
+      </x:c>
+      <x:c r="B71" t="str">
+        <x:v>Faster AI Diffusion Through Hardware-Based Verification</x:v>
+      </x:c>
+      <x:c r="C71" t="str">
+        <x:v>N. Ammann; D. Dalrymple</x:v>
+      </x:c>
+      <x:c r="D71" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="E71" t="str">
+        <x:v>Technical article</x:v>
+      </x:c>
+      <x:c r="F71" t="str">
+        <x:v>Institute for Progress</x:v>
+      </x:c>
+      <x:c r="G71" t="str"/>
+      <x:c r="H71" t="str"/>
+      <x:c r="I71" t="str"/>
+      <x:c r="J71" t="str">
+        <x:v>Motivations and policy proposals</x:v>
+      </x:c>
+      <x:c r="K71" t="str">
+        <x:v>Hardware-enabled verification</x:v>
+      </x:c>
+      <x:c r="L71" t="str">
+        <x:v>hardware-enabled verification; AI diffusion; privacy-preserving verification; guarantee processor; tamper resistance; AI hardware; research and development</x:v>
+      </x:c>
+      <x:c r="M71" t="str">
+        <x:v>Introduces hardware-based, privacy-preserving verification as a way to support wider AI diffusion while limiting misuse, protecting intellectual property, and reducing compliance burdens.</x:v>
+      </x:c>
+      <x:c r="N71" t="str">
+        <x:v>https://ifp.org/faster-ai-diffusion-through-hardware-based-verification/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" t="str">
+        <x:v>dean-verification-plan</x:v>
+      </x:c>
+      <x:c r="B72" t="str">
+        <x:v>Verification Plan</x:v>
+      </x:c>
+      <x:c r="C72" t="str">
+        <x:v>R. Dean</x:v>
+      </x:c>
+      <x:c r="D72" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E72" t="str">
+        <x:v>Technical article</x:v>
+      </x:c>
+      <x:c r="F72" t="str">
+        <x:v>AI 2040</x:v>
+      </x:c>
+      <x:c r="G72" t="str"/>
+      <x:c r="H72" t="str"/>
+      <x:c r="I72" t="str"/>
+      <x:c r="J72" t="str">
+        <x:v>Motivations and policy proposals</x:v>
+      </x:c>
+      <x:c r="K72" t="str">
+        <x:v>International verification regime</x:v>
+      </x:c>
+      <x:c r="L72" t="str">
+        <x:v>international agreements; AI slowdown; compute declaration; inference-only verification; network taps; partial recomputation; chip tracking; covert compute</x:v>
+      </x:c>
+      <x:c r="M72" t="str">
+        <x:v>Proposes a phased verification plan for an international AI slowdown agreement, combining compute accounting, mutual declarations, inference-only retrofits, network taps, and partial recomputation.</x:v>
+      </x:c>
+      <x:c r="N72" t="str">
+        <x:v>https://ai-2040.com/supplements/verification-plan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" t="str">
+        <x:v>wang-nanozk</x:v>
+      </x:c>
+      <x:c r="B73" t="str">
+        <x:v>NanoZK: Privacy-Preserving Verifiable Inference for Large Language Models via Layerwise Zero-Knowledge Proofs</x:v>
+      </x:c>
+      <x:c r="C73" t="str">
+        <x:v>Z. Wang</x:v>
+      </x:c>
+      <x:c r="D73" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E73" t="str">
+        <x:v>Conference</x:v>
+      </x:c>
+      <x:c r="F73" t="str">
+        <x:v>International Conference on Information and Communications Security (ICICS 2026)</x:v>
+      </x:c>
+      <x:c r="G73" t="str">
+        <x:v>10.48550/arXiv.2603.18046</x:v>
+      </x:c>
+      <x:c r="H73" t="str">
+        <x:v>2603.18046</x:v>
+      </x:c>
+      <x:c r="I73" t="str"/>
+      <x:c r="J73" t="str">
+        <x:v>Zero-knowledge proofs</x:v>
+      </x:c>
+      <x:c r="K73" t="str">
+        <x:v>Large-language-model inference</x:v>
+      </x:c>
+      <x:c r="L73" t="str">
+        <x:v>zero-knowledge proofs; large language models; verifiable inference; layerwise proofs; model privacy; activation privacy; Halo2; transformer inference</x:v>
+      </x:c>
+      <x:c r="M73" t="str">
+        <x:v>Introduces a layerwise zero-knowledge proof framework for verifying large-language-model inference while hiding model weights and activations from verifiers.</x:v>
+      </x:c>
+      <x:c r="N73" t="str">
+        <x:v>https://arxiv.org/abs/2603.18046</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:N1"/>
@@ -3236,7 +3314,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a19dc0edf444d01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14a787f4a40f407c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3280,13 +3358,13 @@
         <x:v>Total entries</x:v>
       </x:c>
       <x:c r="B4" s="51" t="n">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D4" s="50" t="str">
         <x:v>Motivations and policy proposals</x:v>
       </x:c>
       <x:c r="E4" s="51" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3352,13 +3430,13 @@
         <x:v>Preprint</x:v>
       </x:c>
       <x:c r="B10" s="51" t="n">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D10" s="50" t="str">
         <x:v>Zero-knowledge proofs</x:v>
       </x:c>
       <x:c r="E10" s="51" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -3366,7 +3444,7 @@
         <x:v>Conference</x:v>
       </x:c>
       <x:c r="B11" s="51" t="n">
-        <x:v>13</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D11" s="50" t="str">
         <x:v>Proof of learning and training</x:v>
@@ -4262,54 +4340,54 @@
       </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="33" t="n">
-        <x:v>11</x:v>
+      <x:c r="A47" s="33" t="str">
+        <x:v>Repository update</x:v>
       </x:c>
       <x:c r="B47" s="27" t="str">
-        <x:v>International Governance of Civilian AI</x:v>
+        <x:v>Faster AI Diffusion Through Hardware-Based Verification</x:v>
       </x:c>
       <x:c r="C47" s="27" t="str">
-        <x:v>The source citation previously contained the invalid identifier 2308.155142.</x:v>
+        <x:v>Added as an introductory resource and bibliography entry.</x:v>
       </x:c>
       <x:c r="D47" s="27" t="str">
-        <x:v>The corrected arXiv identifier 2308.15514 and complete author list from the official record are used.</x:v>
+        <x:v>Recorded as a 2025 technical article by N. Ammann and D. Dalrymple, published by the Institute for Progress.</x:v>
       </x:c>
       <x:c r="E47" s="34" t="str">
-        <x:v>https://arxiv.org/abs/2308.15514</x:v>
+        <x:v>https://ifp.org/faster-ai-diffusion-through-hardware-based-verification/</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="33" t="n">
-        <x:v>11</x:v>
+      <x:c r="A48" s="33" t="str">
+        <x:v>Repository update</x:v>
       </x:c>
       <x:c r="B48" s="27" t="str">
-        <x:v>An International Agreement to Prevent the Premature Creation of Artificial Superintelligence</x:v>
+        <x:v>Verification Plan</x:v>
       </x:c>
       <x:c r="C48" s="27" t="str">
-        <x:v>The reading list labels the work as 2026, but the official arXiv record states that it was submitted in November 2025.</x:v>
+        <x:v>Added to Motivations and policy proposals.</x:v>
       </x:c>
       <x:c r="D48" s="27" t="str">
-        <x:v>Year recorded as 2025 based on the official publication record, not inferred solely from the identifier.</x:v>
+        <x:v>Recorded as a 2026 technical article by R. Dean, published as an AI 2040 supplement.</x:v>
       </x:c>
       <x:c r="E48" s="34" t="str">
-        <x:v>https://arxiv.org/abs/2511.10783</x:v>
+        <x:v>https://ai-2040.com/supplements/verification-plan</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="33" t="n">
-        <x:v>11</x:v>
+      <x:c r="A49" s="33" t="str">
+        <x:v>Repository update</x:v>
       </x:c>
       <x:c r="B49" s="27" t="str">
-        <x:v>On restraining AI development for the sake of safety</x:v>
+        <x:v>NanoZK: Privacy-Preserving Verifiable Inference for Large Language Models via Layerwise Zero-Knowledge Proofs</x:v>
       </x:c>
       <x:c r="C49" s="27" t="str">
-        <x:v>The reading list links through a generic Substack URL.</x:v>
+        <x:v>Added to the zero-knowledge-proofs section.</x:v>
       </x:c>
       <x:c r="D49" s="27" t="str">
-        <x:v>The author's canonical website page, dated 19 March 2026, is used.</x:v>
+        <x:v>Recorded as a 2026 ICICS conference paper and extended arXiv version by Z. Wang.</x:v>
       </x:c>
       <x:c r="E49" s="34" t="str">
-        <x:v>https://joecarlsmith.com/2026/03/19/on-restraining-ai-development-for-the-sake-of-safety/</x:v>
+        <x:v>https://arxiv.org/abs/2603.18046</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
